--- a/tables/AttenuatorDiconPassport.xlsx
+++ b/tables/AttenuatorDiconPassport.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5144C3E0-7546-462B-B9DE-2F4DE79FC5BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-13080" yWindow="1785" windowWidth="14400" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -345,1148 +346,1148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.442</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.44</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.439</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.437</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.434</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.41</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.38</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.375</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.372</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.372</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.372</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0.374</v>
+      </c>
+      <c r="B22" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0.442</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="B3">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="B4">
-        <v>0.439</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="B5">
-        <v>0.437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="B6">
-        <v>0.434</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="B7">
-        <v>0.42899999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="B8">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0.378</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>0.42499999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="B9">
-        <v>0.41899999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="B10">
-        <v>0.41399999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="B11">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="B12">
-        <v>0.40300000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B13">
-        <v>0.39800000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="B14">
-        <v>0.39300000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="B15">
-        <v>0.38900000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="B16">
-        <v>0.38300000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="B17">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="B18">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="B19">
-        <v>0.372</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="B20">
-        <v>0.372</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="B21">
-        <v>0.372</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>0.374</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>1.05</v>
-      </c>
-      <c r="B23">
-        <v>0.378</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B24">
-        <v>0.38500000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="B25">
-        <v>0.39600000000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="B26">
-        <v>0.40899999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="B27" s="1">
         <v>1.25</v>
       </c>
-      <c r="B27">
-        <v>0.42499999999999999</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="B28" s="1">
         <v>1.3</v>
       </c>
-      <c r="B28">
-        <v>0.44600000000000001</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="B29" s="1">
         <v>1.35</v>
       </c>
-      <c r="B29">
-        <v>0.47099999999999997</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30">
+        <v>0.502</v>
+      </c>
+      <c r="B30" s="1">
         <v>1.4</v>
       </c>
-      <c r="B30">
-        <v>0.502</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="B31" s="1">
         <v>1.45</v>
       </c>
-      <c r="B31">
-        <v>0.53600000000000003</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="B32" s="1">
         <v>1.5</v>
       </c>
-      <c r="B32">
-        <v>0.57499999999999996</v>
-      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33">
+        <v>0.62</v>
+      </c>
+      <c r="B33" s="1">
         <v>1.55</v>
       </c>
-      <c r="B33">
-        <v>0.62</v>
-      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="B34" s="1">
         <v>1.6</v>
       </c>
-      <c r="B34">
-        <v>0.67100000000000004</v>
-      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="B35" s="1">
         <v>1.65</v>
       </c>
-      <c r="B35">
-        <v>0.72799999999999998</v>
-      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="A36">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="B36" s="1">
         <v>1.7</v>
       </c>
-      <c r="B36">
-        <v>0.79300000000000004</v>
-      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="A37">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="B37" s="1">
         <v>1.75</v>
       </c>
-      <c r="B37">
-        <v>0.86499999999999999</v>
-      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="A38">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="B38" s="1">
         <v>1.8</v>
       </c>
-      <c r="B38">
-        <v>0.94299999999999995</v>
-      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="A39">
+        <v>1.03</v>
+      </c>
+      <c r="B39" s="1">
         <v>1.85</v>
       </c>
-      <c r="B39">
-        <v>1.03</v>
-      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40">
+        <v>1.1259999999999999</v>
+      </c>
+      <c r="B40" s="1">
         <v>1.9</v>
       </c>
-      <c r="B40">
-        <v>1.1259999999999999</v>
-      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="A41">
+        <v>1.2310000000000001</v>
+      </c>
+      <c r="B41" s="1">
         <v>1.95</v>
       </c>
-      <c r="B41">
-        <v>1.2310000000000001</v>
-      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="A42">
+        <v>1.3460000000000001</v>
+      </c>
+      <c r="B42" s="1">
         <v>2</v>
       </c>
-      <c r="B42">
-        <v>1.3460000000000001</v>
-      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="A43">
+        <v>1.468</v>
+      </c>
+      <c r="B43" s="1">
         <v>2.0499999999999998</v>
       </c>
-      <c r="B43">
-        <v>1.468</v>
-      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="A44">
+        <v>1.6020000000000001</v>
+      </c>
+      <c r="B44" s="1">
         <v>2.1</v>
       </c>
-      <c r="B44">
-        <v>1.6020000000000001</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="A45">
+        <v>1.7490000000000001</v>
+      </c>
+      <c r="B45" s="1">
         <v>2.15</v>
       </c>
-      <c r="B45">
-        <v>1.7490000000000001</v>
-      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="A46">
+        <v>1.905</v>
+      </c>
+      <c r="B46" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B46">
-        <v>1.905</v>
-      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="A47">
+        <v>2.0710000000000002</v>
+      </c>
+      <c r="B47" s="1">
         <v>2.25</v>
       </c>
-      <c r="B47">
-        <v>2.0710000000000002</v>
-      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="A48">
+        <v>2.2519999999999998</v>
+      </c>
+      <c r="B48" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B48">
-        <v>2.2519999999999998</v>
-      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="A49">
+        <v>2.4409999999999998</v>
+      </c>
+      <c r="B49" s="1">
         <v>2.35</v>
       </c>
-      <c r="B49">
-        <v>2.4409999999999998</v>
-      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="A50">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="B50" s="1">
         <v>2.4</v>
       </c>
-      <c r="B50">
-        <v>2.6459999999999999</v>
-      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="A51">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="B51" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="B51">
-        <v>2.8620000000000001</v>
-      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="A52">
+        <v>3.093</v>
+      </c>
+      <c r="B52" s="1">
         <v>2.5</v>
       </c>
-      <c r="B52">
-        <v>3.093</v>
-      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="A53">
+        <v>3.3380000000000001</v>
+      </c>
+      <c r="B53" s="1">
         <v>2.5499999999999998</v>
       </c>
-      <c r="B53">
-        <v>3.3380000000000001</v>
-      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="A54">
+        <v>3.597</v>
+      </c>
+      <c r="B54" s="1">
         <v>2.6</v>
       </c>
-      <c r="B54">
-        <v>3.597</v>
-      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="A55">
+        <v>3.871</v>
+      </c>
+      <c r="B55" s="1">
         <v>2.65</v>
       </c>
-      <c r="B55">
-        <v>3.871</v>
-      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="A56">
+        <v>4.1609999999999996</v>
+      </c>
+      <c r="B56" s="1">
         <v>2.7</v>
       </c>
-      <c r="B56">
-        <v>4.1609999999999996</v>
-      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="A57">
+        <v>4.4669999999999996</v>
+      </c>
+      <c r="B57" s="1">
         <v>2.75</v>
       </c>
-      <c r="B57">
-        <v>4.4669999999999996</v>
-      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="A58">
+        <v>4.7889999999999997</v>
+      </c>
+      <c r="B58" s="1">
         <v>2.8</v>
       </c>
-      <c r="B58">
-        <v>4.7889999999999997</v>
-      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="A59">
+        <v>5.1260000000000003</v>
+      </c>
+      <c r="B59" s="1">
         <v>2.85</v>
       </c>
-      <c r="B59">
-        <v>5.1260000000000003</v>
-      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="A60">
+        <v>5.4790000000000001</v>
+      </c>
+      <c r="B60" s="1">
         <v>2.9</v>
       </c>
-      <c r="B60">
-        <v>5.4790000000000001</v>
-      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="A61">
+        <v>5.851</v>
+      </c>
+      <c r="B61" s="1">
         <v>2.95</v>
       </c>
-      <c r="B61">
-        <v>5.851</v>
-      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="A62">
+        <v>6.2389999999999999</v>
+      </c>
+      <c r="B62" s="1">
         <v>3</v>
       </c>
-      <c r="B62">
-        <v>6.2389999999999999</v>
-      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="A63">
+        <v>6.6429999999999998</v>
+      </c>
+      <c r="B63" s="1">
         <v>3.05</v>
       </c>
-      <c r="B63">
-        <v>6.6429999999999998</v>
-      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="A64">
+        <v>7.0640000000000001</v>
+      </c>
+      <c r="B64" s="1">
         <v>3.1</v>
       </c>
-      <c r="B64">
-        <v>7.0640000000000001</v>
-      </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="A65">
+        <v>7.5039999999999996</v>
+      </c>
+      <c r="B65" s="1">
         <v>3.15</v>
       </c>
-      <c r="B65">
-        <v>7.5039999999999996</v>
-      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="A66">
+        <v>7.9589999999999996</v>
+      </c>
+      <c r="B66" s="1">
         <v>3.2</v>
       </c>
-      <c r="B66">
-        <v>7.9589999999999996</v>
-      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="A67">
+        <v>8.4339999999999993</v>
+      </c>
+      <c r="B67" s="1">
         <v>3.25</v>
       </c>
-      <c r="B67">
-        <v>8.4339999999999993</v>
-      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="A68">
+        <v>8.9239999999999995</v>
+      </c>
+      <c r="B68" s="1">
         <v>3.3</v>
       </c>
-      <c r="B68">
-        <v>8.9239999999999995</v>
-      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+      <c r="A69">
+        <v>9.43</v>
+      </c>
+      <c r="B69" s="1">
         <v>3.35</v>
       </c>
-      <c r="B69">
-        <v>9.43</v>
-      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+      <c r="A70">
+        <v>9.9670000000000005</v>
+      </c>
+      <c r="B70" s="1">
         <v>3.4</v>
       </c>
-      <c r="B70">
-        <v>9.9670000000000005</v>
-      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="A71">
+        <v>10.51</v>
+      </c>
+      <c r="B71" s="1">
         <v>3.45</v>
       </c>
-      <c r="B71">
-        <v>10.51</v>
-      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="A72">
+        <v>11.071</v>
+      </c>
+      <c r="B72" s="1">
         <v>3.5</v>
       </c>
-      <c r="B72">
-        <v>11.071</v>
-      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="A73">
+        <v>11.648</v>
+      </c>
+      <c r="B73" s="1">
         <v>3.55</v>
       </c>
-      <c r="B73">
-        <v>11.648</v>
-      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+      <c r="A74">
+        <v>12.241</v>
+      </c>
+      <c r="B74" s="1">
         <v>3.6</v>
       </c>
-      <c r="B74">
-        <v>12.241</v>
-      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="A75">
+        <v>12.852</v>
+      </c>
+      <c r="B75" s="1">
         <v>3.65</v>
       </c>
-      <c r="B75">
-        <v>12.852</v>
-      </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+      <c r="A76">
+        <v>13.476000000000001</v>
+      </c>
+      <c r="B76" s="1">
         <v>3.7</v>
       </c>
-      <c r="B76">
-        <v>13.476000000000001</v>
-      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+      <c r="A77">
+        <v>14.117000000000001</v>
+      </c>
+      <c r="B77" s="1">
         <v>3.75</v>
       </c>
-      <c r="B77">
-        <v>14.117000000000001</v>
-      </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="A78">
+        <v>14.773</v>
+      </c>
+      <c r="B78" s="1">
         <v>3.8</v>
       </c>
-      <c r="B78">
-        <v>14.773</v>
-      </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+      <c r="A79">
+        <v>15.449</v>
+      </c>
+      <c r="B79" s="1">
         <v>3.85</v>
       </c>
-      <c r="B79">
-        <v>15.449</v>
-      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="A80">
+        <v>16.138999999999999</v>
+      </c>
+      <c r="B80" s="1">
         <v>3.9</v>
       </c>
-      <c r="B80">
-        <v>16.138999999999999</v>
-      </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="A81">
+        <v>16.841000000000001</v>
+      </c>
+      <c r="B81" s="1">
         <v>3.95</v>
       </c>
-      <c r="B81">
-        <v>16.841000000000001</v>
-      </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+      <c r="A82">
+        <v>17.556999999999999</v>
+      </c>
+      <c r="B82" s="1">
         <v>4</v>
       </c>
-      <c r="B82">
-        <v>17.556999999999999</v>
-      </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+      <c r="A83">
+        <v>18.294</v>
+      </c>
+      <c r="B83" s="1">
         <v>4.05</v>
       </c>
-      <c r="B83">
-        <v>18.294</v>
-      </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+      <c r="A84">
+        <v>19.041</v>
+      </c>
+      <c r="B84" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B84">
-        <v>19.041</v>
-      </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="A85">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="B85" s="1">
         <v>4.1500000000000004</v>
       </c>
-      <c r="B85">
-        <v>19.809999999999999</v>
-      </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="A86">
+        <v>20.597999999999999</v>
+      </c>
+      <c r="B86" s="1">
         <v>4.2</v>
       </c>
-      <c r="B86">
-        <v>20.597999999999999</v>
-      </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="A87">
+        <v>21.402000000000001</v>
+      </c>
+      <c r="B87" s="1">
         <v>4.25</v>
       </c>
-      <c r="B87">
-        <v>21.402000000000001</v>
-      </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="A88">
+        <v>22.236000000000001</v>
+      </c>
+      <c r="B88" s="1">
         <v>4.3</v>
       </c>
-      <c r="B88">
-        <v>22.236000000000001</v>
-      </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+      <c r="A89">
+        <v>23.085000000000001</v>
+      </c>
+      <c r="B89" s="1">
         <v>4.3499999999999996</v>
       </c>
-      <c r="B89">
-        <v>23.085000000000001</v>
-      </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+      <c r="A90">
+        <v>23.966000000000001</v>
+      </c>
+      <c r="B90" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="B90">
-        <v>23.966000000000001</v>
-      </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="A91">
+        <v>24.87</v>
+      </c>
+      <c r="B91" s="1">
         <v>4.45</v>
       </c>
-      <c r="B91">
-        <v>24.87</v>
-      </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="A92">
+        <v>25.812999999999999</v>
+      </c>
+      <c r="B92" s="1">
         <v>4.5</v>
       </c>
-      <c r="B92">
-        <v>25.812999999999999</v>
-      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="A93">
+        <v>26.795000000000002</v>
+      </c>
+      <c r="B93" s="1">
         <v>4.55</v>
       </c>
-      <c r="B93">
-        <v>26.795000000000002</v>
-      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+      <c r="A94">
+        <v>27.82</v>
+      </c>
+      <c r="B94" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B94">
-        <v>27.82</v>
-      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+      <c r="A95">
+        <v>28.895</v>
+      </c>
+      <c r="B95" s="1">
         <v>4.6500000000000004</v>
       </c>
-      <c r="B95">
-        <v>28.895</v>
-      </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+      <c r="A96">
+        <v>30.033000000000001</v>
+      </c>
+      <c r="B96" s="1">
         <v>4.7</v>
       </c>
-      <c r="B96">
-        <v>30.033000000000001</v>
-      </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+      <c r="A97">
+        <v>31.231000000000002</v>
+      </c>
+      <c r="B97" s="1">
         <v>4.75</v>
       </c>
-      <c r="B97">
-        <v>31.231000000000002</v>
-      </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+      <c r="A98">
+        <v>32.503</v>
+      </c>
+      <c r="B98" s="1">
         <v>4.8</v>
       </c>
-      <c r="B98">
-        <v>32.503</v>
-      </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+      <c r="A99">
+        <v>33.866</v>
+      </c>
+      <c r="B99" s="1">
         <v>4.8499999999999996</v>
       </c>
-      <c r="B99">
-        <v>33.866</v>
-      </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+      <c r="A100">
+        <v>35.325000000000003</v>
+      </c>
+      <c r="B100" s="1">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B100">
-        <v>35.325000000000003</v>
-      </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+      <c r="A101">
+        <v>36.898000000000003</v>
+      </c>
+      <c r="B101" s="1">
         <v>4.95</v>
       </c>
-      <c r="B101">
-        <v>36.898000000000003</v>
-      </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
+      <c r="A102">
+        <v>38.621000000000002</v>
+      </c>
+      <c r="B102" s="1">
         <v>5</v>
       </c>
-      <c r="B102">
-        <v>38.621000000000002</v>
-      </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="A103">
+        <v>40.515999999999998</v>
+      </c>
+      <c r="B103" s="1">
         <v>5.05</v>
       </c>
-      <c r="B103">
-        <v>40.515999999999998</v>
-      </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
+      <c r="A104">
+        <v>42.628</v>
+      </c>
+      <c r="B104" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B104">
-        <v>42.628</v>
-      </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+      <c r="A105">
+        <v>45.014000000000003</v>
+      </c>
+      <c r="B105" s="1">
         <v>5.15</v>
       </c>
-      <c r="B105">
-        <v>45.014000000000003</v>
-      </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+      <c r="A106">
+        <v>47.777000000000001</v>
+      </c>
+      <c r="B106" s="1">
         <v>5.2</v>
       </c>
-      <c r="B106">
-        <v>47.777000000000001</v>
-      </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="A107">
+        <v>51.076999999999998</v>
+      </c>
+      <c r="B107" s="1">
         <v>5.25</v>
       </c>
-      <c r="B107">
-        <v>51.076999999999998</v>
-      </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="A108">
+        <v>55.112000000000002</v>
+      </c>
+      <c r="B108" s="1">
         <v>5.3</v>
       </c>
-      <c r="B108">
-        <v>55.112000000000002</v>
-      </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+      <c r="A109">
+        <v>59.972999999999999</v>
+      </c>
+      <c r="B109" s="1">
         <v>5.35</v>
       </c>
-      <c r="B109">
-        <v>59.972999999999999</v>
-      </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+      <c r="A110">
+        <v>63.085999999999999</v>
+      </c>
+      <c r="B110" s="1">
         <v>5.4</v>
       </c>
-      <c r="B110">
-        <v>63.085999999999999</v>
-      </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+      <c r="A111">
+        <v>61.332999999999998</v>
+      </c>
+      <c r="B111" s="1">
         <v>5.45</v>
       </c>
-      <c r="B111">
-        <v>61.332999999999998</v>
-      </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+      <c r="A112">
+        <v>59.195</v>
+      </c>
+      <c r="B112" s="1">
         <v>5.5</v>
       </c>
-      <c r="B112">
-        <v>59.195</v>
-      </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+      <c r="A113">
+        <v>58.006999999999998</v>
+      </c>
+      <c r="B113" s="1">
         <v>5.55</v>
       </c>
-      <c r="B113">
-        <v>58.006999999999998</v>
-      </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+      <c r="A114">
+        <v>57.642000000000003</v>
+      </c>
+      <c r="B114" s="1">
         <v>5.6</v>
       </c>
-      <c r="B114">
-        <v>57.642000000000003</v>
-      </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+      <c r="A115">
+        <v>57.935000000000002</v>
+      </c>
+      <c r="B115" s="1">
         <v>5.65</v>
       </c>
-      <c r="B115">
-        <v>57.935000000000002</v>
-      </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+      <c r="A116">
+        <v>58.808999999999997</v>
+      </c>
+      <c r="B116" s="1">
         <v>5.7</v>
       </c>
-      <c r="B116">
-        <v>58.808999999999997</v>
-      </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
+      <c r="A117">
+        <v>60.162999999999997</v>
+      </c>
+      <c r="B117" s="1">
         <v>5.75</v>
       </c>
-      <c r="B117">
-        <v>60.162999999999997</v>
-      </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+      <c r="A118">
+        <v>61.662999999999997</v>
+      </c>
+      <c r="B118" s="1">
         <v>5.8</v>
       </c>
-      <c r="B118">
-        <v>61.662999999999997</v>
-      </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+      <c r="A119">
+        <v>62.17</v>
+      </c>
+      <c r="B119" s="1">
         <v>5.85</v>
       </c>
-      <c r="B119">
-        <v>62.17</v>
-      </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="A120">
+        <v>60.773000000000003</v>
+      </c>
+      <c r="B120" s="1">
         <v>5.9</v>
       </c>
-      <c r="B120">
-        <v>60.773000000000003</v>
-      </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+      <c r="A121">
+        <v>58.436</v>
+      </c>
+      <c r="B121" s="1">
         <v>5.95</v>
       </c>
-      <c r="B121">
-        <v>58.436</v>
-      </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+      <c r="A122">
+        <v>56.173999999999999</v>
+      </c>
+      <c r="B122" s="1">
         <v>6</v>
       </c>
-      <c r="B122">
-        <v>56.173999999999999</v>
-      </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+      <c r="A123">
+        <v>54.281999999999996</v>
+      </c>
+      <c r="B123" s="1">
         <v>6.05</v>
       </c>
-      <c r="B123">
-        <v>54.281999999999996</v>
-      </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+      <c r="A124">
+        <v>52.747999999999998</v>
+      </c>
+      <c r="B124" s="1">
         <v>6.1</v>
       </c>
-      <c r="B124">
-        <v>52.747999999999998</v>
-      </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
+      <c r="A125">
+        <v>51.515999999999998</v>
+      </c>
+      <c r="B125" s="1">
         <v>6.15</v>
       </c>
-      <c r="B125">
-        <v>51.515999999999998</v>
-      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+      <c r="A126">
+        <v>50.548000000000002</v>
+      </c>
+      <c r="B126" s="1">
         <v>6.2</v>
       </c>
-      <c r="B126">
-        <v>50.548000000000002</v>
-      </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
+      <c r="A127">
+        <v>49.804000000000002</v>
+      </c>
+      <c r="B127" s="1">
         <v>6.25</v>
       </c>
-      <c r="B127">
-        <v>49.804000000000002</v>
-      </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
+      <c r="A128">
+        <v>49.256</v>
+      </c>
+      <c r="B128" s="1">
         <v>6.3</v>
       </c>
-      <c r="B128">
-        <v>49.256</v>
-      </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
+      <c r="A129">
+        <v>48.886000000000003</v>
+      </c>
+      <c r="B129" s="1">
         <v>6.35</v>
       </c>
-      <c r="B129">
-        <v>48.886000000000003</v>
-      </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
+      <c r="A130">
+        <v>48.677</v>
+      </c>
+      <c r="B130" s="1">
         <v>6.4</v>
       </c>
-      <c r="B130">
-        <v>48.677</v>
-      </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+      <c r="A131">
+        <v>48.618000000000002</v>
+      </c>
+      <c r="B131" s="1">
         <v>6.45</v>
       </c>
-      <c r="B131">
-        <v>48.618000000000002</v>
-      </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
+      <c r="A132">
+        <v>48.695</v>
+      </c>
+      <c r="B132" s="1">
         <v>6.5</v>
       </c>
-      <c r="B132">
-        <v>48.695</v>
-      </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
+      <c r="A133">
+        <v>48.898000000000003</v>
+      </c>
+      <c r="B133" s="1">
         <v>6.55</v>
       </c>
-      <c r="B133">
-        <v>48.898000000000003</v>
-      </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
+      <c r="A134">
+        <v>49.213000000000001</v>
+      </c>
+      <c r="B134" s="1">
         <v>6.6</v>
       </c>
-      <c r="B134">
-        <v>49.213000000000001</v>
-      </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
+      <c r="A135">
+        <v>49.622999999999998</v>
+      </c>
+      <c r="B135" s="1">
         <v>6.65</v>
       </c>
-      <c r="B135">
-        <v>49.622999999999998</v>
-      </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
+      <c r="A136">
+        <v>50.09</v>
+      </c>
+      <c r="B136" s="1">
         <v>6.7</v>
       </c>
-      <c r="B136">
-        <v>50.09</v>
-      </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
+      <c r="A137">
+        <v>50.575000000000003</v>
+      </c>
+      <c r="B137" s="1">
         <v>6.75</v>
       </c>
-      <c r="B137">
-        <v>50.575000000000003</v>
-      </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="1">
+      <c r="A138">
+        <v>51.017000000000003</v>
+      </c>
+      <c r="B138" s="1">
         <v>6.8</v>
       </c>
-      <c r="B138">
-        <v>51.017000000000003</v>
-      </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="1">
+      <c r="A139">
+        <v>51.337000000000003</v>
+      </c>
+      <c r="B139" s="1">
         <v>6.85</v>
       </c>
-      <c r="B139">
-        <v>51.337000000000003</v>
-      </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
+      <c r="A140">
+        <v>51.460999999999999</v>
+      </c>
+      <c r="B140" s="1">
         <v>6.9</v>
       </c>
-      <c r="B140">
-        <v>51.460999999999999</v>
-      </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="1">
+      <c r="A141">
+        <v>51.351999999999997</v>
+      </c>
+      <c r="B141" s="1">
         <v>6.95</v>
       </c>
-      <c r="B141">
-        <v>51.351999999999997</v>
-      </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="1">
+      <c r="A142">
+        <v>51.023000000000003</v>
+      </c>
+      <c r="B142" s="1">
         <v>7</v>
-      </c>
-      <c r="B142">
-        <v>51.023000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/tables/AttenuatorDiconPassport.xlsx
+++ b/tables/AttenuatorDiconPassport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5144C3E0-7546-462B-B9DE-2F4DE79FC5BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3384844F-5900-4B98-B47B-0404D51651E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13080" yWindow="1785" windowWidth="14400" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>Voltage (V)</t>
   </si>
   <si>
-    <t>Attenuation (dBm)</t>
+    <t>Attenuation (dB)</t>
   </si>
 </sst>
 </file>
